--- a/config/achievement/achievement_task.xlsx
+++ b/config/achievement/achievement_task.xlsx
@@ -1561,7 +1561,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>見習い調査員</t>
+          <t>见习调查员</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv40に到達</t>
+          <t>伙伴达到Lv40</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>初級調査員</t>
+          <t>初级调查员</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="Q5" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv60に到達</t>
+          <t>伙伴达到Lv60</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>中級調査員</t>
+          <t>中级调查员</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv80に到達</t>
+          <t>伙伴达到Lv80</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>上級調査員</t>
+          <t>高级调查员</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv99に到達</t>
+          <t>伙伴达到Lv99</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>特級調査員</t>
+          <t>特级调查员</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv104に到達</t>
+          <t>伙伴达到Lv104</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>秘紋調査員</t>
+          <t>秘纹调查员</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv109に到達</t>
+          <t>伙伴到达Lv109</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>覚醒調査員</t>
+          <t>觉醒调查员</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv114に到達</t>
+          <t>伙伴到达Lv114</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>超越調査員</t>
+          <t>超越调查员</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>仲間がLv119に到達</t>
+          <t>伙伴到达Lv119</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>新米の冒険者</t>
+          <t>新手冒险家</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>ランセンスがLv3に到達</t>
+          <t>许可证达到Lv3</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>熟練冒険者</t>
+          <t>熟练的冒险家</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>ランセンスがLv6に到達</t>
+          <t>运行达到Lv6</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>一流冒険者</t>
+          <t>一流冒险家</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>ランセンスがLv9に到達</t>
+          <t>许可证达到Lv9</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>伝説の冒険者</t>
+          <t>传说中的冒险家</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>ランセンスがLv12に到達</t>
+          <t>运行状态达到Lv12</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>訓練の序</t>
+          <t>训练·序</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>特権属性が合計でLv20に到達</t>
+          <t>特权属性合计达到Lv20</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>訓練の破</t>
+          <t>训练·破</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>特権属性が合計でLv50に到達</t>
+          <t>特权属性合计达到Lv50</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>訓練の急</t>
+          <t>训练·急</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>特権属性が合計でLv100に到達</t>
+          <t>特权属性合计达到Lv100</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>覚醒の刻</t>
+          <t>觉醒时刻</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>特権属性が合計でLv300に到達</t>
+          <t>特权属性合计达到Lv300</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>基礎天賦Ⅰ</t>
+          <t>基础天赋Ⅰ</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>基礎天賦に天賦Ptを60消費</t>
+          <t>基础天赋消耗60点天赋Pt</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>基礎天賦Ⅱ</t>
+          <t>基础天赋Ⅱ</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>基礎天賦に天賦Ptを120消費</t>
+          <t>基础天赋消耗120点天赋Pt</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>基礎天賦Ⅲ</t>
+          <t>基础天赋Ⅲ</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>基礎天賦に天賦Ptを240消費</t>
+          <t>基础天赋消耗240点天赋Pt</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>昇格天賦Ⅰ</t>
+          <t>晋升天赋Ⅰ</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>昇格天賦に天賦Ptを100消費</t>
+          <t>升级天赋消耗100点天赋Pt</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>昇格天賦Ⅱ</t>
+          <t>晋升天赋Ⅱ</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
-          <t>昇格天賦に天賦Ptを200消費</t>
+          <t>升级天赋消耗200点天赋Pt</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>昇格天賦Ⅲ</t>
+          <t>晋升天赋Ⅲ</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>昇格天賦に天賦Ptを400消費</t>
+          <t>升级天赋消耗400点天赋Pt</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>属性天賦Ⅰ</t>
+          <t>属性天赋Ⅰ</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
-          <t>属性天賦に天賦Ptを100消費</t>
+          <t>属性天赋消耗100点天赋Pt</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>属性天賦Ⅱ</t>
+          <t>属性天赋Ⅱ</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>属性天賦に天賦Ptを200消費</t>
+          <t>属性天赋消耗200点天赋Pt</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>属性天賦Ⅲ</t>
+          <t>属性天赋Ⅲ</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
-          <t>属性天賦に天賦Ptを400消費</t>
+          <t>属性天赋消耗400点天赋Pt</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>属性天賦Ⅳ</t>
+          <t>属性天赋Ⅳ</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>属性天賦に天賦Ptを800消費</t>
+          <t>属性天赋消耗800点天赋Pt</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>属性天賦Ⅴ</t>
+          <t>属性天赋Ⅴ</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
-          <t>属性天賦に天賦Ptを1600消費</t>
+          <t>属性天赋消耗1600点天赋Pt</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>天賦レベルⅠ</t>
+          <t>天赋等级Ⅰ</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>合計で天賦Ptを200消費</t>
+          <t>合计消耗200点天赋Pt</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>天賦レベルⅡ</t>
+          <t>天赋等级Ⅱ</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
-          <t>合計で天賦Ptを500消費</t>
+          <t>合计消耗500点天赋Pt</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>天賦レベルⅢ</t>
+          <t>天赋等级Ⅲ</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>合計で天賦Ptを1000消費</t>
+          <t>合计消耗1000点天赋Pt</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>天賦レベルⅣ</t>
+          <t>天赋等级Ⅳ</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>合計で天賦Ptを2000消費</t>
+          <t>合计消耗2000点天赋Pt</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>メカⅠ</t>
+          <t>机械Ⅰ</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>探査機を3個解放</t>
+          <t>释放3个探测器</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>メカⅡ</t>
+          <t>机械Ⅱ</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>探査機を6個解放</t>
+          <t>释放6个探测器</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>メカⅢ</t>
+          <t>机械Ⅲ</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>探査機を9個解放</t>
+          <t>释放9个探测器</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>メカⅣ</t>
+          <t>机械Ⅳ</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>探査機を12個解放</t>
+          <t>释放12个探测器</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>機動型-γ</t>
+          <t>机动型-γ</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>機動型-γを解放</t>
+          <t>机动型-γ解放</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>飛行型-γ</t>
+          <t>飞行型-γ</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>飛行型-γを解放</t>
+          <t>释放飞行型-γ</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>火力型-δを解放</t>
+          <t>火力型-释放δ</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>究極型-δ</t>
+          <t>终极型-δ</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>究極型-δを解放</t>
+          <t>终极型-释放δ</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>機装士Ⅰ</t>
+          <t>机装士Ⅰ</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="Q43" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv3に到達</t>
+          <t>任何探测器到达Lv3</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>機装士Ⅱ</t>
+          <t>机装士Ⅱ</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="Q44" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv6に到達</t>
+          <t>任何探测器到达Lv6</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>機装士Ⅲ</t>
+          <t>机装士Ⅲ</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="Q45" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv9に到達</t>
+          <t>任何探测器到达Lv9</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>機装士Ⅳ</t>
+          <t>机装士Ⅳ</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="Q46" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv12に到達</t>
+          <t>任何探测器到达Lv12</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>機装士Ⅴ</t>
+          <t>机装士Ⅴ</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="Q47" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv15に到達</t>
+          <t>任何探测器到达Lv15</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>機装士Ⅵ</t>
+          <t>机装士Ⅵ</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="Q48" s="7" t="inlineStr">
         <is>
-          <t>任意の探査機がLv20に到達</t>
+          <t>任何探测器到达Lv20</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅰ</t>
+          <t>调查员Ⅰ</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が100000に到達</t>
+          <t>角色战力达到100000</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅱ</t>
+          <t>调查员Ⅱ</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が200000に到達</t>
+          <t>角色战力达到200000</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅲ</t>
+          <t>调查员Ⅲ</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が500000に到達</t>
+          <t>角色战力达到500000</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅳ</t>
+          <t>调查员Ⅳ</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が1000000に到達</t>
+          <t>角色战力达到1000000</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅴ</t>
+          <t>调查员Ⅴ</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が1500000に到達</t>
+          <t>角色战力达到1500000</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>調査員Ⅵ</t>
+          <t>调查员Ⅵ</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
-          <t>キャラの戦力が2000000に到達</t>
+          <t>角色战力达到2000万</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅰ</t>
+          <t>金币获得Ⅰ</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>金貨を3000000獲得</t>
+          <t>获得3万金币</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅱ</t>
+          <t>金币获得Ⅱ</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>金貨を6000000獲得</t>
+          <t>获得6000000金币</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅲ</t>
+          <t>金币获得Ⅲ</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>金貨を15000000獲得</t>
+          <t>获得15,000金币</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅳ</t>
+          <t>金币获得Ⅳ</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
-          <t>金貨を30000000獲得</t>
+          <t>获得30000000金币</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅴ</t>
+          <t>金币获得Ⅴ</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>金貨を60000000獲得</t>
+          <t>获得60000000金币</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅵ</t>
+          <t>金币获得Ⅵ</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
-          <t>金貨を150000000獲得</t>
+          <t>获得150000000金币</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅶ</t>
+          <t>金币获得Ⅶ</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>金貨を300000000獲得</t>
+          <t>获得300000金币</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅷ</t>
+          <t>金币获得Ⅷ</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
-          <t>金貨を600000000獲得</t>
+          <t>获得60亿金币</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>金貨獲得Ⅸ</t>
+          <t>金币获得Ⅸ</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>金貨を1500000000獲得</t>
+          <t>获得1500000金币</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅰ</t>
+          <t>硬币消费Ⅰ</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>累計で3000000金貨を消費</t>
+          <t>累计消耗3000000金币</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅱ</t>
+          <t>硬币消费Ⅱ</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>累計で6000000金貨を消費</t>
+          <t>累计消耗6000000金币</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅲ</t>
+          <t>硬币消费Ⅲ</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Q66" s="4" t="inlineStr">
         <is>
-          <t>累計で15000000金貨を消費</t>
+          <t>累计消耗15000000金币</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅳ</t>
+          <t>硬币消费Ⅳ</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>累計で30000000金貨を消費</t>
+          <t>累计消耗30000000金币</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅴ</t>
+          <t>硬币消费Ⅴ</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="Q68" s="4" t="inlineStr">
         <is>
-          <t>累計で60000000金貨を消費</t>
+          <t>累计消耗60000000金币</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅵ</t>
+          <t>硬币消费Ⅵ</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Q69" s="4" t="inlineStr">
         <is>
-          <t>累計で150000000金貨を消費</t>
+          <t>累计消耗150000000金币</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅶ</t>
+          <t>硬币消费Ⅶ</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>累計で300000000金貨を消費</t>
+          <t>累计消耗300000000金币</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅷ</t>
+          <t>硬币消费Ⅷ</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>累計で600000000金貨を消費</t>
+          <t>累计消耗600000000金币</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>コイン消費Ⅸ</t>
+          <t>硬币消费Ⅸ</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="Q72" s="4" t="inlineStr">
         <is>
-          <t>累計で1500000000金貨を消費</t>
+          <t>累计消耗1500000000金币</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅰ</t>
+          <t>钻石获得Ⅰ</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを5000獲得</t>
+          <t>获得5000颗钻石</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅱ</t>
+          <t>钻石获得Ⅱ</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを10000獲得</t>
+          <t>获得10000颗钻石</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅲ</t>
+          <t>钻石获得Ⅲ</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを20000獲得</t>
+          <t>获得20000颗钻石</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅳ</t>
+          <t>钻石获得Ⅳ</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを50000獲得</t>
+          <t>获得50000颗钻石</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅴ</t>
+          <t>钻石获得Ⅴ</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを100000獲得</t>
+          <t>获得100000颗钻石</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅵ</t>
+          <t>钻石获得Ⅵ</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを200000獲得</t>
+          <t>获得200000颗钻石</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅶ</t>
+          <t>钻石获得Ⅶ</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを500000獲得</t>
+          <t>获得500000颗钻石</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅷ</t>
+          <t>钻石获得Ⅷ</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを1000000獲得</t>
+          <t>获得10万颗钻石</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>ダイヤ獲得Ⅸ</t>
+          <t>钻石获得Ⅸ</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>ダイヤを5000000獲得</t>
+          <t>获得5000万颗钻石</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅰ</t>
+          <t>累计消费Ⅰ</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>累計で5000ダイヤを消費</t>
+          <t>累计消费5000颗钻石</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅱ</t>
+          <t>累计消费Ⅱ</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>累計で10000ダイヤを消費</t>
+          <t>累计消耗10000颗钻石</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅲ</t>
+          <t>累计消费Ⅲ</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="Q84" s="4" t="inlineStr">
         <is>
-          <t>累計で20000ダイヤを消費</t>
+          <t>累计消耗20000颗钻石</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅳ</t>
+          <t>累计消费Ⅳ</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="Q85" s="4" t="inlineStr">
         <is>
-          <t>累計で50000ダイヤを消費</t>
+          <t>累计消费50000钻石</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅴ</t>
+          <t>累计消费Ⅴ</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="Q86" s="4" t="inlineStr">
         <is>
-          <t>累計で100000ダイヤを消費</t>
+          <t>累计消耗100000颗钻石</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅵ</t>
+          <t>累计消费Ⅵ</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="Q87" s="4" t="inlineStr">
         <is>
-          <t>累計で200000ダイヤを消費</t>
+          <t>累计消耗200000颗钻石</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅶ</t>
+          <t>累计消费Ⅶ</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="Q88" s="4" t="inlineStr">
         <is>
-          <t>累計で500000ダイヤを消費</t>
+          <t>累计消耗500000颗钻石</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅷ</t>
+          <t>累计消费Ⅷ</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>累計で1000000ダイヤを消費</t>
+          <t>累计消耗10万颗钻石</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>累計消費Ⅸ</t>
+          <t>累计消费Ⅸ</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>累計で5000000ダイヤを消費</t>
+          <t>累计消耗5000万颗钻石</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>特権アップ</t>
+          <t>特权提升</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>特権ステータスPtがLv600に達する</t>
+          <t>特权状态Pt达到Lv600</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>特権アップ</t>
+          <t>特权提升</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="Q92" s="4" t="inlineStr">
         <is>
-          <t>特権ステータスPtがLv1000に達する</t>
+          <t>特权状态Pt达到Lv1000</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>MAX強化Ⅰ</t>
+          <t>MAX强化Ⅰ</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>任意の仲間の全能力値をMAXまで強化</t>
+          <t>将任意伙伴的全能力值强化至最大</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>MAX強化Ⅱ</t>
+          <t>MAX强化Ⅱ</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="Q95" s="4" t="inlineStr">
         <is>
-          <t>10体の仲間の全能力値をMAXまで強化</t>
+          <t>将10位伙伴的全能力值强化至MAX</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>絆の力</t>
+          <t>羁绊的力量</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="Q96" s="4" t="inlineStr">
         <is>
-          <t>祈願センターで累計300個の欠片を送信</t>
+          <t>祈愿中心累计发送300个碎片</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="Q97" s="4" t="inlineStr">
         <is>
-          <t>厳選ショップを累計1000回手動更新</t>
+          <t>精选商店累计手动更新1000次</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>神秘商店を累計300回手動更新</t>
+          <t>神秘商店累计手动更新300次</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>ルーンの品質</t>
+          <t>符文的质量</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="Q99" s="4" t="inlineStr">
         <is>
-          <t>任意の仲間のルーン品質が2200に到達</t>
+          <t>任意伙伴的符文质量达到2200</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>赤·ルーン収集</t>
+          <t>红色符文收集</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="Q100" s="4" t="inlineStr">
         <is>
-          <t>赤·ルーンを累計100個獲得</t>
+          <t>累计获得100个红色符文</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅰ</t>
+          <t>图鉴解放Ⅰ</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="Q102" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を10体解放</t>
+          <t>在图鉴中解放10位伙伴</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅱ</t>
+          <t>图鉴解放Ⅱ</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を25体解放</t>
+          <t>在图鉴中解放25位伙伴</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅲ</t>
+          <t>图鉴解放Ⅲ</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11093,7 +11093,7 @@
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を50体解放</t>
+          <t>在图鉴中解放50位伙伴</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅳ</t>
+          <t>图鉴解放Ⅳ</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を100体解放</t>
+          <t>在图鉴中解放100位伙伴</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅴ</t>
+          <t>图鉴解放Ⅴ</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="Q106" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を150体解放</t>
+          <t>在图鉴中解放150名伙伴</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅵ</t>
+          <t>图鉴解放Ⅵ</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を200体解放</t>
+          <t>在图鉴中解放200名伙伴</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅶ</t>
+          <t>图鉴解放Ⅶ</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="Q108" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を250体解放</t>
+          <t>在图鉴中解放250名伙伴</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>図鑑解放Ⅷ</t>
+          <t>图鉴解放Ⅷ</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>図鑑で仲間を300体解放</t>
+          <t>通过图鉴解放300名伙伴</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>無·属性の仲間を5体獲得</t>
+          <t>获得5个无属性伙伴</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="Q111" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を10体獲得</t>
+          <t>获得10个无属性伙伴</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を15体獲得</t>
+          <t>获得15个无属性伙伴</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="Q113" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を20体獲得</t>
+          <t>获得20个无属性伙伴</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を30体獲得</t>
+          <t>获得30个无属性伙伴</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="Q115" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を5体獲得</t>
+          <t>获得5个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="Q116" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を10体獲得</t>
+          <t>获得10个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="Q117" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を15体獲得</t>
+          <t>获得15个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を20体獲得</t>
+          <t>获得20个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="Q119" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を30体獲得</t>
+          <t>获得30个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="Q120" s="5" t="inlineStr">
         <is>
-          <t>水·属性の仲間を5体獲得</t>
+          <t>获得5个水、属性伙伴</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>水·属性の仲間を10体獲得</t>
+          <t>获得10个水、属性伙伴</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="Q122" s="5" t="inlineStr">
         <is>
-          <t>水·属性の仲間を15体獲得</t>
+          <t>获得15个水、属性伙伴</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>水·属性の仲間を20体獲得</t>
+          <t>获得20个水属性伙伴</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="Q124" s="5" t="inlineStr">
         <is>
-          <t>水·属性の仲間を30体獲得</t>
+          <t>获得30个水、属性伙伴</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="Q125" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を5体獲得</t>
+          <t>获得5个木属性伙伴</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を10体獲得</t>
+          <t>获得10个木属性伙伴</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="Q127" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を15体獲得</t>
+          <t>获得15个木属性伙伴</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="Q128" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を20体獲得</t>
+          <t>获得20个木属性伙伴</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="Q129" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を30体獲得</t>
+          <t>获得30个木属性伙伴</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="Q130" s="5" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を5体獲得</t>
+          <t>获得5个雷属性伙伴</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を10体獲得</t>
+          <t>获得10个雷属性伙伴</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
@@ -13904,7 +13904,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="Q132" s="5" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を15体獲得</t>
+          <t>获得15个雷属性伙伴</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を20体獲得</t>
+          <t>获得20个雷属性伙伴</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を30体獲得</t>
+          <t>获得30个雷属性伙伴</t>
         </is>
       </c>
       <c r="R134" t="inlineStr">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="Q135" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を5体獲得</t>
+          <t>获得5个寒属性伙伴</t>
         </is>
       </c>
       <c r="R135" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="Q136" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を10体獲得</t>
+          <t>获得10个寒属性伙伴</t>
         </is>
       </c>
       <c r="R136" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="Q137" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を15体獲得</t>
+          <t>获得15个寒属性伙伴</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を20体獲得</t>
+          <t>获得20个寒属性伙伴</t>
         </is>
       </c>
       <c r="R138" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="Q139" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を30体獲得</t>
+          <t>获得30个寒属性伙伴</t>
         </is>
       </c>
       <c r="R139" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="Q140" s="5" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を5体獲得</t>
+          <t>获得5个战属性伙伴</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を10体獲得</t>
+          <t>获得10个战属性伙伴</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="Q142" s="5" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を15体獲得</t>
+          <t>获得15个战属性伙伴</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="Q143" s="5" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を20体獲得</t>
+          <t>获得20个战属性伙伴</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="Q144" s="5" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を30体獲得</t>
+          <t>获得30个战属性伙伴</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="Q145" s="5" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を5体獲得</t>
+          <t>获得5个毒属性伙伴</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="Q146" s="5" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を10体獲得</t>
+          <t>获得10个毒属性伙伴</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="Q147" s="5" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を15体獲得</t>
+          <t>获得15个毒属性伙伴</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="Q148" s="5" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を20体獲得</t>
+          <t>获得20个毒属性伙伴</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="Q149" s="5" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を30体獲得</t>
+          <t>获得30个毒属性伙伴</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="Q150" s="5" t="inlineStr">
         <is>
-          <t>地·属性の仲間を5体獲得</t>
+          <t>获得5个地属性伙伴</t>
         </is>
       </c>
       <c r="R150" s="10" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="Q151" s="5" t="inlineStr">
         <is>
-          <t>地·属性の仲間を10体獲得</t>
+          <t>获得10个地·属性的伙伴</t>
         </is>
       </c>
       <c r="R151" s="10" t="inlineStr">
@@ -15944,7 +15944,7 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="Q152" s="5" t="inlineStr">
         <is>
-          <t>地·属性の仲間を15体獲得</t>
+          <t>获得15个地、属性伙伴</t>
         </is>
       </c>
       <c r="R152" s="10" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="Q153" s="5" t="inlineStr">
         <is>
-          <t>地·属性の仲間を20体獲得</t>
+          <t>获得20个地、属性伙伴</t>
         </is>
       </c>
       <c r="R153" s="10" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="Q154" s="5" t="inlineStr">
         <is>
-          <t>地·属性の仲間を30体獲得</t>
+          <t>获得30个地、属性伙伴</t>
         </is>
       </c>
       <c r="R154" s="10" t="inlineStr">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="Q155" s="5" t="inlineStr">
         <is>
-          <t>空·属性の仲間を5体獲得</t>
+          <t>获得5个空属性伙伴</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Q156" s="5" t="inlineStr">
         <is>
-          <t>空·属性の仲間を10体獲得</t>
+          <t>获得10个空属性伙伴</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="Q157" s="5" t="inlineStr">
         <is>
-          <t>空·属性の仲間を15体獲得</t>
+          <t>获得15个空属性伙伴</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="Q158" s="5" t="inlineStr">
         <is>
-          <t>空·属性の仲間を20体獲得</t>
+          <t>获得20个空属性伙伴</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="Q159" s="5" t="inlineStr">
         <is>
-          <t>空·属性の仲間を30体獲得</t>
+          <t>获得30个空属性伙伴</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
@@ -16760,7 +16760,7 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="Q160" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を5体獲得</t>
+          <t>获得5个法属性伙伴</t>
         </is>
       </c>
       <c r="R160" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="Q161" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を10体獲得</t>
+          <t>获得10个法属性伙伴</t>
         </is>
       </c>
       <c r="R161" t="inlineStr">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="Q162" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を15体獲得</t>
+          <t>获得15个法、属性伙伴</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="Q163" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を20体獲得</t>
+          <t>获得20个法属性伙伴</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -17168,7 +17168,7 @@
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を30体獲得</t>
+          <t>获得30个法属性伙伴</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="Q165" s="5" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を5体獲得</t>
+          <t>获得5个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -17372,7 +17372,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="Q166" s="5" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を10体獲得</t>
+          <t>获得10个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="Q167" s="5" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を15体獲得</t>
+          <t>获得15个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="Q168" s="5" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を20体獲得</t>
+          <t>获得20个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="Q169" s="5" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を30体獲得</t>
+          <t>获得30个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="Q170" s="5" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を5体獲得</t>
+          <t>获得5个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="Q171" s="5" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を10体獲得</t>
+          <t>获得10个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="Q172" s="5" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を15体獲得</t>
+          <t>获得15个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="Q173" s="5" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を20体獲得</t>
+          <t>获得20个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="Q174" s="5" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を30体獲得</t>
+          <t>获得30个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="Q175" s="9" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を5体獲得</t>
+          <t>获得5个黑暗、属性的伙伴</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を10体獲得</t>
+          <t>获得10个黑暗、属性的伙伴</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="Q177" s="9" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を15体獲得</t>
+          <t>获得15个黑暗、属性伙伴</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="Q178" s="9" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を20体獲得</t>
+          <t>获得20个黑暗、属性伙伴</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="Q179" s="9" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を30体獲得</t>
+          <t>获得30个黑暗、属性伙伴</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="Q180" s="5" t="inlineStr">
         <is>
-          <t>神·属性の仲間を5体獲得</t>
+          <t>获得5个神属性伙伴</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="Q181" s="5" t="inlineStr">
         <is>
-          <t>神·属性の仲間を10体獲得</t>
+          <t>获得10个神属性伙伴</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="Q182" s="5" t="inlineStr">
         <is>
-          <t>神·属性の仲間を15体獲得</t>
+          <t>获得15个神属性伙伴</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="Q183" s="5" t="inlineStr">
         <is>
-          <t>神·属性の仲間を20体獲得</t>
+          <t>获得20个神属性伙伴</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="Q184" s="5" t="inlineStr">
         <is>
-          <t>神·属性の仲間を30体獲得</t>
+          <t>获得30个神属性伙伴</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -19310,7 +19310,7 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="Q185" s="5" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を5体獲得</t>
+          <t>获得5个邪属性伙伴</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -19412,7 +19412,7 @@
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="Q186" s="5" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を10体獲得</t>
+          <t>获得10个邪属性伙伴</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="Q187" s="5" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を15体獲得</t>
+          <t>获得15个邪属性伙伴</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="Q188" s="5" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を20体獲得</t>
+          <t>获得20个邪属性伙伴</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -19718,7 +19718,7 @@
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="Q189" s="5" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を30体獲得</t>
+          <t>获得30个邪属性伙伴</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="Q190" s="5" t="inlineStr">
         <is>
-          <t>金·属性の仲間を5体獲得</t>
+          <t>获得5个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="Q191" s="5" t="inlineStr">
         <is>
-          <t>金·属性の仲間を10体獲得</t>
+          <t>获得10个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="Q192" s="5" t="inlineStr">
         <is>
-          <t>金·属性の仲間を15体獲得</t>
+          <t>获得15个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="Q193" s="5" t="inlineStr">
         <is>
-          <t>金·属性の仲間を20体獲得</t>
+          <t>获得20个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="Q194" s="5" t="inlineStr">
         <is>
-          <t>金·属性の仲間を30体獲得</t>
+          <t>获得30个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="Q195" s="11" t="inlineStr">
         <is>
-          <t>精·属性の仲間を5体獲得</t>
+          <t>获得5个精、属性伙伴</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="Q196" s="11" t="inlineStr">
         <is>
-          <t>精·属性の仲間を10体獲得</t>
+          <t>获得10个精、属性伙伴</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -20559,7 +20559,7 @@
       </c>
       <c r="Q197" s="12" t="inlineStr">
         <is>
-          <t>精·属性の仲間を15体獲得</t>
+          <t>获得15个精、属性伙伴</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="Q198" s="12" t="inlineStr">
         <is>
-          <t>精·属性の仲間を20体獲得</t>
+          <t>获得20个精、属性伙伴</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -20763,7 +20763,7 @@
       </c>
       <c r="Q199" s="12" t="inlineStr">
         <is>
-          <t>精·属性の仲間を30体獲得</t>
+          <t>获得30个精、属性伙伴</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅰ</t>
+          <t>图鉴的全部解放Ⅰ</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="Q200" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を350体解放</t>
+          <t>在图鉴中解放350名伙伴</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅱ</t>
+          <t>图鉴的全部解放Ⅱ</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="Q201" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を400体解放</t>
+          <t>在图鉴中解放400名伙伴</t>
         </is>
       </c>
       <c r="R201" t="inlineStr">
@@ -21034,7 +21034,7 @@
       </c>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅲ</t>
+          <t>图鉴的全部解放Ⅲ</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -21059,7 +21059,7 @@
       </c>
       <c r="Q202" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を450体解放</t>
+          <t>在图鉴中解放450名伙伴</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅳ</t>
+          <t>图鉴的全部解放Ⅳ</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -21161,7 +21161,7 @@
       </c>
       <c r="Q203" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を500体解放</t>
+          <t>通过图鉴解放500名伙伴</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅴ</t>
+          <t>图鉴的全部解放Ⅴ</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="Q204" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を550体解放</t>
+          <t>在图鉴中解放550名伙伴</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>図鑑の全解放Ⅵ</t>
+          <t>图鉴的全部解放Ⅵ</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -21365,7 +21365,7 @@
       </c>
       <c r="Q205" s="4" t="inlineStr">
         <is>
-          <t>図鑑で仲間を600体解放</t>
+          <t>在图鉴中解放600名伙伴</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="Q206" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を10体獲得</t>
+          <t>获得10个无属性伙伴</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -21554,7 +21554,7 @@
       </c>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -21579,7 +21579,7 @@
       </c>
       <c r="Q207" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を60体獲得</t>
+          <t>获得60个无属性伙伴</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>無·属性コレクター</t>
+          <t>无属性收藏家</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="Q208" s="9" t="inlineStr">
         <is>
-          <t>無·属性の仲間を80体獲得</t>
+          <t>获得80个无属性伙伴</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="Q209" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を40体獲得</t>
+          <t>获得40个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="Q210" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を60体獲得</t>
+          <t>获得60个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>炎·属性コレクター</t>
+          <t>火焰属性收藏家</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="Q211" s="9" t="inlineStr">
         <is>
-          <t>炎·属性の仲間を80体獲得</t>
+          <t>获得80个火焰、属性伙伴</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="Q212" s="4" t="inlineStr">
         <is>
-          <t>水·属性の仲間を40体獲得</t>
+          <t>获得40个水、属性伙伴</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="Q213" s="4" t="inlineStr">
         <is>
-          <t>水·属性の仲間を60体獲得</t>
+          <t>获得60个水、属性伙伴</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -22303,7 +22303,7 @@
       </c>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>水·属性コレクター</t>
+          <t>水和属性收集器</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
@@ -22328,7 +22328,7 @@
       </c>
       <c r="Q214" s="4" t="inlineStr">
         <is>
-          <t>水·属性の仲間を80体獲得</t>
+          <t>获得80个水、属性伙伴</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -22410,7 +22410,7 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="Q215" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を40体獲得</t>
+          <t>获得40个木属性伙伴</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="Q216" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を60体獲得</t>
+          <t>获得60个木属性伙伴</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>木·属性コレクター</t>
+          <t>树木属性收藏家</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="Q217" s="9" t="inlineStr">
         <is>
-          <t>木·属性の仲間を80体獲得</t>
+          <t>获得80个木属性伙伴</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -22756,7 +22756,7 @@
       </c>
       <c r="Q218" s="4" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を40体獲得</t>
+          <t>获得40个雷、属性伙伴</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -22838,7 +22838,7 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>雷·属性コレクター</t>
+          <t>雷电属性收藏家</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
@@ -22863,7 +22863,7 @@
       </c>
       <c r="Q219" s="4" t="inlineStr">
         <is>
-          <t>雷·属性の仲間を60体獲得</t>
+          <t>获得60个雷属性伙伴</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -22945,7 +22945,7 @@
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>寒·属性コレクター</t>
+          <t>冷属性收藏家</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="Q220" s="9" t="inlineStr">
         <is>
-          <t>寒·属性の仲間を40体獲得</t>
+          <t>获得40个寒属性伙伴</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -23077,7 +23077,7 @@
       </c>
       <c r="Q221" s="4" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を40体獲得</t>
+          <t>获得40个战属性伙伴</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>戦·属性コレクター</t>
+          <t>属性收集者</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="Q222" s="4" t="inlineStr">
         <is>
-          <t>戦·属性の仲間を50体獲得</t>
+          <t>获得50个战属性伙伴</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="Q223" s="4" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を40体獲得</t>
+          <t>获得40个毒属性伙伴</t>
         </is>
       </c>
       <c r="R223" t="inlineStr">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>毒·属性コレクター</t>
+          <t>毒药和属性收藏家</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="Q224" s="4" t="inlineStr">
         <is>
-          <t>毒·属性の仲間を60体獲得</t>
+          <t>获得60个毒属性伙伴</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="Q225" s="9" t="inlineStr">
         <is>
-          <t>地·属性の仲間を40体獲得</t>
+          <t>获得40个地、属性伙伴</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>地·属性コレクター</t>
+          <t>属性收集器</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="Q226" s="9" t="inlineStr">
         <is>
-          <t>地·属性の仲間を60体獲得</t>
+          <t>获得60个地、属性伙伴</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="Q227" s="4" t="inlineStr">
         <is>
-          <t>空·属性の仲間を40体獲得</t>
+          <t>获得40个空属性伙伴</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -23801,7 +23801,7 @@
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="Q228" s="4" t="inlineStr">
         <is>
-          <t>空·属性の仲間を60体獲得</t>
+          <t>获得60个空属性伙伴</t>
         </is>
       </c>
       <c r="R228" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>空·属性コレクター</t>
+          <t>空属性收集器</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -23933,7 +23933,7 @@
       </c>
       <c r="Q229" s="4" t="inlineStr">
         <is>
-          <t>空·属性の仲間を80体獲得</t>
+          <t>获得80个空属性伙伴</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -24015,7 +24015,7 @@
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="Q230" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を40体獲得</t>
+          <t>获得40个法属性伙伴</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -24122,7 +24122,7 @@
       </c>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="Q231" s="9" t="inlineStr">
         <is>
-          <t>法·属性の仲間を60体獲得</t>
+          <t>获得60个法属性伙伴</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
@@ -24229,7 +24229,7 @@
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>法·属性コレクター</t>
+          <t>法律和属性收藏家</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -24254,7 +24254,7 @@
       </c>
       <c r="Q232" s="13" t="inlineStr">
         <is>
-          <t>法·属性の仲間を80体獲得</t>
+          <t>获得80个法、属性伙伴</t>
         </is>
       </c>
       <c r="R232" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>魅·属性コレクター</t>
+          <t>魅属性收藏家</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -24361,7 +24361,7 @@
       </c>
       <c r="Q233" s="4" t="inlineStr">
         <is>
-          <t>魅·属性の仲間を40体獲得</t>
+          <t>获得40个魅属性的伙伴</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -24443,7 +24443,7 @@
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -24468,7 +24468,7 @@
       </c>
       <c r="Q234" s="4" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を40体獲得</t>
+          <t>获得40个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>岩·属性コレクター</t>
+          <t>岩石和属性收藏家</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -24575,7 +24575,7 @@
       </c>
       <c r="Q235" s="4" t="inlineStr">
         <is>
-          <t>岩·属性の仲間を60体獲得</t>
+          <t>获得60个岩石、属性伙伴</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -24657,7 +24657,7 @@
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>暗·属性コレクター</t>
+          <t>黑暗属性收藏家</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -24682,7 +24682,7 @@
       </c>
       <c r="Q236" s="13" t="inlineStr">
         <is>
-          <t>暗·属性の仲間を50体獲得</t>
+          <t>获得50个黑暗、属性伙伴</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>神·属性コレクター</t>
+          <t>神属性收藏家</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="Q237" s="4" t="inlineStr">
         <is>
-          <t>神·属性の仲間を50体獲得</t>
+          <t>获得50个神属性伙伴</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>邪·属性コレクター</t>
+          <t>邪属性收藏家</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="Q238" s="4" t="inlineStr">
         <is>
-          <t>邪·属性の仲間を50体獲得</t>
+          <t>获得50个邪属性伙伴</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>金·属性コレクター</t>
+          <t>黄金属性收藏家</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="Q239" s="4" t="inlineStr">
         <is>
-          <t>金·属性の仲間を50体獲得</t>
+          <t>获得50个黄金、属性伙伴</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>精·属性コレクター</t>
+          <t>精属性收藏家</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="Q240" s="13" t="inlineStr">
         <is>
-          <t>精·属性の仲間を50体獲得</t>
+          <t>获得50个精、属性伙伴</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -25190,7 +25190,7 @@
       </c>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -25215,7 +25215,7 @@
       </c>
       <c r="Q242" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体がLv30に到達</t>
+          <t>任意6名伙伴达到Lv30</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -25317,7 +25317,7 @@
       </c>
       <c r="Q243" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体がLv30に到達</t>
+          <t>任意10名伙伴达到Lv30</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="Q244" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体がLv50に到達</t>
+          <t>任意6名伙伴达到Lv50</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -25521,7 +25521,7 @@
       </c>
       <c r="Q245" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体がLv50に到達</t>
+          <t>任意10位伙伴达到Lv50</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -25598,7 +25598,7 @@
       </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="Q246" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体がLv65に到達</t>
+          <t>任意6名伙伴达到Lv65</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="Q247" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体がLv65に到達</t>
+          <t>任意10名伙伴达到Lv65</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="Q248" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体がLv80に到達</t>
+          <t>任意6名伙伴达到Lv80</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="Q249" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体がLv80に到達</t>
+          <t>任意10名伙伴达到Lv80</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -26031,7 +26031,7 @@
       </c>
       <c r="Q250" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体がLv100に到達</t>
+          <t>任意6名伙伴到达Lv100</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>仲間のレベルアップ</t>
+          <t>伙伴的等级提升</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -26133,7 +26133,7 @@
       </c>
       <c r="Q251" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体がLv100に到達</t>
+          <t>任意10位伙伴到达Lv100</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -26210,7 +26210,7 @@
       </c>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -26235,7 +26235,7 @@
       </c>
       <c r="Q252" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体が青品質に到達</t>
+          <t>任意6名伙伴达到蓝色品质</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -26312,7 +26312,7 @@
       </c>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -26337,7 +26337,7 @@
       </c>
       <c r="Q253" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体が青品質に到達</t>
+          <t>任意10名伙伴达到蓝色品质</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -26439,7 +26439,7 @@
       </c>
       <c r="Q254" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体が紫品質に到達</t>
+          <t>任意6名伙伴达到紫色品质</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -26541,7 +26541,7 @@
       </c>
       <c r="Q255" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体が紫品質に到達</t>
+          <t>任意10名伙伴达到紫色品质</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -26618,7 +26618,7 @@
       </c>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="Q256" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間6体が橙品質に到達</t>
+          <t>任意6名伙伴达到橙品质</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -26720,7 +26720,7 @@
       </c>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>仲間の突破</t>
+          <t>伙伴的突破</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -26745,7 +26745,7 @@
       </c>
       <c r="Q257" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間10体が橙品質に到達</t>
+          <t>任意10名伙伴达到橙品质</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -26822,7 +26822,7 @@
       </c>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -26847,7 +26847,7 @@
       </c>
       <c r="Q258" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星4に到達</t>
+          <t>6名伙伴到达4星</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="Q259" s="5" t="inlineStr">
         <is>
-          <t>10体の仲間が星4に到達</t>
+          <t>10名伙伴到达4星</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="Q260" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星5に到達</t>
+          <t>6名伙伴到达5星</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -27128,7 +27128,7 @@
       </c>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="Q261" s="5" t="inlineStr">
         <is>
-          <t>10体の仲間が星5に到達</t>
+          <t>10名伙伴到达5星</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -27255,7 +27255,7 @@
       </c>
       <c r="Q262" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星7に到達</t>
+          <t>6名伙伴到达7星</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -27357,7 +27357,7 @@
       </c>
       <c r="Q263" s="5" t="inlineStr">
         <is>
-          <t>10体の仲間が星7に到達</t>
+          <t>10名伙伴到达7星</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -27434,7 +27434,7 @@
       </c>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="Q264" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星9に到達</t>
+          <t>6名伙伴到达9星</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="Q265" s="5" t="inlineStr">
         <is>
-          <t>10体の仲間が星9に到達</t>
+          <t>10名伙伴到达9星</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -27663,7 +27663,7 @@
       </c>
       <c r="Q266" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星10に到達</t>
+          <t>6名伙伴到达10星</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -27740,7 +27740,7 @@
       </c>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -27765,7 +27765,7 @@
       </c>
       <c r="Q267" s="5" t="inlineStr">
         <is>
-          <t>10体の仲間が星10に到達</t>
+          <t>10名伙伴到达10星</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="Q268" s="5" t="inlineStr">
         <is>
-          <t>1体の仲間が星12に到達</t>
+          <t>1名伙伴到达12星</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="Q269" s="5" t="inlineStr">
         <is>
-          <t>6体の仲間が星12に到達</t>
+          <t>6名伙伴到达星12</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -28061,7 +28061,7 @@
       </c>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>仲間の星ランク</t>
+          <t>伙伴星级</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -28086,7 +28086,7 @@
       </c>
       <c r="Q270" s="5" t="inlineStr">
         <is>
-          <t>20体の仲間が星12に到達</t>
+          <t>20名伙伴到达星12</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -28158,7 +28158,7 @@
       </c>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -28183,7 +28183,7 @@
       </c>
       <c r="Q271" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を100回育成(通常)</t>
+          <t>培养任意伙伴强化值100次（通常）</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -28255,7 +28255,7 @@
       </c>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="Q272" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を500回育成(通常)</t>
+          <t>培养任意伙伴500次强化值（通常）</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -28352,7 +28352,7 @@
       </c>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -28377,7 +28377,7 @@
       </c>
       <c r="Q273" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を1000回育成(通常)</t>
+          <t>培养任意伙伴1000次强化值（通常）</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="Q274" s="4" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を100回育成(通常)</t>
+          <t>培养任意伙伴强化值100次（通常）</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -28546,7 +28546,7 @@
       </c>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="Q275" s="4" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を500回育成(通常)</t>
+          <t>培养任意伙伴500次强化值（通常）</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>仲間の強化値育成</t>
+          <t>伙伴的强化值育成</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -28668,7 +28668,7 @@
       </c>
       <c r="Q276" s="4" t="inlineStr">
         <is>
-          <t>任意の仲間の強化値を1000回育成(通常)</t>
+          <t>培养任意伙伴1000次强化值（通常）</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -28745,7 +28745,7 @@
       </c>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="Q277" s="5" t="inlineStr">
         <is>
-          <t>12体の仲間の装飾が青品質に到達</t>
+          <t>12名伙伴装饰达到蓝色品质</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="Q278" s="5" t="inlineStr">
         <is>
-          <t>24体の仲間の装飾が青品質に到達</t>
+          <t>24名伙伴装饰达到蓝色品质</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -28949,7 +28949,7 @@
       </c>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="Q279" s="5" t="inlineStr">
         <is>
-          <t>12体の仲間の装飾が紫品質に到達</t>
+          <t>12名伙伴的装饰达到紫色品质</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -29076,7 +29076,7 @@
       </c>
       <c r="Q280" s="5" t="inlineStr">
         <is>
-          <t>24体の仲間の装飾が紫品質に到達</t>
+          <t>24名伙伴装饰达到紫色品质</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="Q281" s="5" t="inlineStr">
         <is>
-          <t>12体の仲間の装飾が橙品質に到達</t>
+          <t>12名伙伴的装饰达到橙品质</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>装飾の強化</t>
+          <t>装饰增强</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="Q282" s="5" t="inlineStr">
         <is>
-          <t>24体の仲間の装飾が橙品質に到達</t>
+          <t>24名伙伴的装饰达到橙品质</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -29357,7 +29357,7 @@
       </c>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>装飾の覚醒</t>
+          <t>装饰的觉醒</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="Q283" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間がLv1の覚醒装飾を4個所持</t>
+          <t>任意伙伴持有4个Lv1觉醒装饰</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>装飾の覚醒</t>
+          <t>装饰的觉醒</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="Q284" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間がLv2の覚醒装飾を4個所持</t>
+          <t>任意伙伴持有4个Lv2觉醒装饰</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -29561,7 +29561,7 @@
       </c>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>装飾の覚醒</t>
+          <t>装饰的觉醒</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -29586,7 +29586,7 @@
       </c>
       <c r="Q285" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間がLv3の覚醒装飾を4個所持</t>
+          <t>任意伙伴持有4个Lv3觉醒装饰</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -29663,7 +29663,7 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>装飾の覚醒</t>
+          <t>装饰的觉醒</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="Q286" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間がLv4の覚醒装飾を4個所持</t>
+          <t>任意伙伴拥有4个Lv4觉醒装饰</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -29770,7 +29770,7 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>装飾の覚醒</t>
+          <t>装饰的觉醒</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="Q287" s="5" t="inlineStr">
         <is>
-          <t>任意の仲間がLv5の覚醒装飾を4個所持</t>
+          <t>任意伙伴持有4个Lv5觉醒装饰</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>装備の収集</t>
+          <t>装备收集</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="Q288" s="5" t="inlineStr">
         <is>
-          <t>Lv1の装備アイテムを6個所持</t>
+          <t>持有6个Lv1装备道具</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>装備の収集</t>
+          <t>装备收集</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -29999,7 +29999,7 @@
       </c>
       <c r="Q289" s="5" t="inlineStr">
         <is>
-          <t>Lv5の装備アイテムを6個所持</t>
+          <t>持有6个Lv5装备道具</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>装備の収集</t>
+          <t>装备收集</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -30101,7 +30101,7 @@
       </c>
       <c r="Q290" s="5" t="inlineStr">
         <is>
-          <t>Lv10の装備アイテムを6個所持</t>
+          <t>持有6个Lv10装备道具</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>装備の収集</t>
+          <t>装备收集</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="Q291" s="5" t="inlineStr">
         <is>
-          <t>Lv20の装備アイテムを6個所持</t>
+          <t>持有6个Lv20装备道具</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>装備の収集</t>
+          <t>装备收集</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -30305,7 +30305,7 @@
       </c>
       <c r="Q292" s="5" t="inlineStr">
         <is>
-          <t>Lv30の装備アイテムを6個所持</t>
+          <t>持有6个Lv30装备道具</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="L293" s="14" t="inlineStr">
         <is>
-          <t>青の装備</t>
+          <t>蓝色装备</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -30407,7 +30407,7 @@
       </c>
       <c r="Q293" s="5" t="inlineStr">
         <is>
-          <t>青·装備アイテムを1個所持</t>
+          <t>蓝色装备道具1个</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -30484,7 +30484,7 @@
       </c>
       <c r="L294" s="14" t="inlineStr">
         <is>
-          <t>紫の装備</t>
+          <t>紫色装备</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="Q294" s="5" t="inlineStr">
         <is>
-          <t>紫·装備アイテムを1個所持</t>
+          <t>紫色装备道具1个</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -30591,7 +30591,7 @@
       </c>
       <c r="L295" s="14" t="inlineStr">
         <is>
-          <t>橙の装備</t>
+          <t>橙色装备</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -30616,7 +30616,7 @@
       </c>
       <c r="Q295" s="5" t="inlineStr">
         <is>
-          <t>橙·装備アイテムを1個所持</t>
+          <t>持有1个橙色装备道具</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -30718,7 +30718,7 @@
       </c>
       <c r="Q296" s="5" t="inlineStr">
         <is>
-          <t>任意6体の仲間好感度がLv50に到達</t>
+          <t>任意6名伙伴好感度达到Lv50</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -30820,7 +30820,7 @@
       </c>
       <c r="Q297" s="5" t="inlineStr">
         <is>
-          <t>任意6体の仲間好感度がLv150に到達</t>
+          <t>任意6名伙伴好感度达到Lv150</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -30922,7 +30922,7 @@
       </c>
       <c r="Q298" s="5" t="inlineStr">
         <is>
-          <t>任意6体の仲間好感度がLv300に到達</t>
+          <t>任意6名伙伴好感度达到Lv300</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -30997,7 +30997,7 @@
       </c>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅰ</t>
+          <t>关卡挑战Ⅰ</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -31022,7 +31022,7 @@
       </c>
       <c r="Q300" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに200回挑戦</t>
+          <t>200次故事模式挑战</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅱ</t>
+          <t>关卡挑战Ⅱ</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -31119,7 +31119,7 @@
       </c>
       <c r="Q301" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに500回挑戦</t>
+          <t>500次故事模式挑战</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -31191,7 +31191,7 @@
       </c>
       <c r="L302" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅲ</t>
+          <t>关卡挑战Ⅲ</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -31216,7 +31216,7 @@
       </c>
       <c r="Q302" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに1000回挑戦</t>
+          <t>1000次故事模式挑战</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅳ</t>
+          <t>关卡挑战Ⅳ</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -31313,7 +31313,7 @@
       </c>
       <c r="Q303" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに2000回挑戦</t>
+          <t>2000次故事模式挑战</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅴ</t>
+          <t>关卡挑战Ⅴ</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -31410,7 +31410,7 @@
       </c>
       <c r="Q304" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに5000回挑戦</t>
+          <t>5000次故事模式挑战</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>ステージ挑戦Ⅵ</t>
+          <t>关卡挑战Ⅵ</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -31512,7 +31512,7 @@
       </c>
       <c r="Q305" s="5" t="inlineStr">
         <is>
-          <t>ストーリーモードに10000回挑戦</t>
+          <t>10000次故事模式挑战</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="L306" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="Q306" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに200回挑戦</t>
+          <t>挑战200次硬模式</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="L307" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -31706,7 +31706,7 @@
       </c>
       <c r="Q307" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに500回挑戦</t>
+          <t>挑战困难模式500次</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -31778,7 +31778,7 @@
       </c>
       <c r="L308" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="Q308" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに1000回挑戦</t>
+          <t>挑战1000次硬模式</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -31875,7 +31875,7 @@
       </c>
       <c r="L309" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="Q309" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに2000回挑戦</t>
+          <t>挑战2000次硬模式</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="L310" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -31997,7 +31997,7 @@
       </c>
       <c r="Q310" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに5000回挑戦</t>
+          <t>挑战困难模式5000次</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -32069,7 +32069,7 @@
       </c>
       <c r="L311" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ挑戦</t>
+          <t>困难关卡挑战</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="Q311" s="5" t="inlineStr">
         <is>
-          <t>ハードモードに10000回挑戦</t>
+          <t>挑战10000次硬模式</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="L312" s="2" t="inlineStr">
         <is>
-          <t>金貨の試練</t>
+          <t>金币的考验</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -32191,7 +32191,7 @@
       </c>
       <c r="Q312" s="5" t="inlineStr">
         <is>
-          <t>金貨ダンジョンで任意のステージを累計100回クリア</t>
+          <t>金币迷宫中任意关卡累计通关100次</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -32263,7 +32263,7 @@
       </c>
       <c r="L313" s="2" t="inlineStr">
         <is>
-          <t>金貨の試練</t>
+          <t>金币的考验</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -32288,7 +32288,7 @@
       </c>
       <c r="Q313" s="5" t="inlineStr">
         <is>
-          <t>金貨ダンジョンで任意のステージを累計500回クリア</t>
+          <t>金币迷宫中任意关卡累计通关500次</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -32360,7 +32360,7 @@
       </c>
       <c r="L314" s="2" t="inlineStr">
         <is>
-          <t>金貨の試練</t>
+          <t>金币的考验</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -32385,7 +32385,7 @@
       </c>
       <c r="Q314" s="5" t="inlineStr">
         <is>
-          <t>金貨ダンジョンで任意のステージを累計1000回クリア</t>
+          <t>金币迷宫中任意关卡累计通关1000次</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="L315" s="2" t="inlineStr">
         <is>
-          <t>経験値の試練</t>
+          <t>经验值的考验</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -32482,7 +32482,7 @@
       </c>
       <c r="Q315" s="5" t="inlineStr">
         <is>
-          <t>経験値ダンジョンで任意のステージを累計100回クリア</t>
+          <t>经验值在迷宫中任意关卡累计通关100次</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -32554,7 +32554,7 @@
       </c>
       <c r="L316" s="2" t="inlineStr">
         <is>
-          <t>経験値の試練</t>
+          <t>经验值的考验</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -32579,7 +32579,7 @@
       </c>
       <c r="Q316" s="5" t="inlineStr">
         <is>
-          <t>経験値ダンジョンで任意のステージを累計500回クリア</t>
+          <t>经验值在地下城中任意关卡累计通关500次</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -32651,7 +32651,7 @@
       </c>
       <c r="L317" s="2" t="inlineStr">
         <is>
-          <t>経験値の試練</t>
+          <t>经验值的考验</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="Q317" s="5" t="inlineStr">
         <is>
-          <t>経験値ダンジョンで任意のステージを累計1000回クリア</t>
+          <t>经验值在地下城中任意关卡累计通关1000次</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -32748,7 +32748,7 @@
       </c>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>ギフトの試練</t>
+          <t>礼物试验</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -32773,7 +32773,7 @@
       </c>
       <c r="Q318" s="5" t="inlineStr">
         <is>
-          <t>ギフトダンジョンで任意のステージを累計100回クリア</t>
+          <t>在礼物地下城中任意关卡累计通关100次</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -32845,7 +32845,7 @@
       </c>
       <c r="L319" s="2" t="inlineStr">
         <is>
-          <t>ギフトの試練</t>
+          <t>礼物试验</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -32870,7 +32870,7 @@
       </c>
       <c r="Q319" s="5" t="inlineStr">
         <is>
-          <t>ギフトダンジョンで任意のステージを累計500回クリア</t>
+          <t>在礼物地下城中任意关卡累计通关500次</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -32942,7 +32942,7 @@
       </c>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>ギフトの試練</t>
+          <t>礼物试验</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -32967,7 +32967,7 @@
       </c>
       <c r="Q320" s="5" t="inlineStr">
         <is>
-          <t>ギフトダンジョンで任意のステージを累計1000回クリア</t>
+          <t>在礼物地下城中任意关卡累计通关1000次</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -33039,7 +33039,7 @@
       </c>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>欠片の試練</t>
+          <t>碎片的考验</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -33064,7 +33064,7 @@
       </c>
       <c r="Q321" s="5" t="inlineStr">
         <is>
-          <t>欠片ダンジョンで任意のステージを累計100回クリア</t>
+          <t>在碎片地下城中任意关卡累计通关100次</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -33136,7 +33136,7 @@
       </c>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>欠片の試練</t>
+          <t>碎片的考验</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -33161,7 +33161,7 @@
       </c>
       <c r="Q322" s="5" t="inlineStr">
         <is>
-          <t>欠片ダンジョンで任意のステージを累計500回クリア</t>
+          <t>在碎片地下城中任意关卡累计通关500次</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>欠片の試練</t>
+          <t>碎片的考验</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="Q323" s="5" t="inlineStr">
         <is>
-          <t>欠片ダンジョンで任意のステージを累計1000回クリア</t>
+          <t>在碎片地下城中任意关卡累计通关1000次</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="L324" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -33360,7 +33360,7 @@
       </c>
       <c r="Q324" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第20ステージをクリア</t>
+          <t>在试炼之路上完成第20关卡</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -33437,7 +33437,7 @@
       </c>
       <c r="L325" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="Q325" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第40ステージをクリア</t>
+          <t>在试炼之路上完成第40关卡</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -33539,7 +33539,7 @@
       </c>
       <c r="L326" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -33564,7 +33564,7 @@
       </c>
       <c r="Q326" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第60ステージをクリア</t>
+          <t>在试炼之路上完成第60关卡</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="L327" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -33666,7 +33666,7 @@
       </c>
       <c r="Q327" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第80ステージをクリア</t>
+          <t>在试炼之路上完成第80关卡</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -33748,7 +33748,7 @@
       </c>
       <c r="L328" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -33773,7 +33773,7 @@
       </c>
       <c r="Q328" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第100ステージをクリア</t>
+          <t>在试炼之路上完成第100关卡</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -33850,7 +33850,7 @@
       </c>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -33875,7 +33875,7 @@
       </c>
       <c r="Q329" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第110ステージをクリア</t>
+          <t>在试炼之路上完成第110关卡</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -33952,7 +33952,7 @@
       </c>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="Q330" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第120ステージをクリア</t>
+          <t>在试炼之路上完成第120关卡</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -34054,7 +34054,7 @@
       </c>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -34079,7 +34079,7 @@
       </c>
       <c r="Q331" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第130ステージをクリア</t>
+          <t>在试炼之路上完成第130关卡</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -34156,7 +34156,7 @@
       </c>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="Q332" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第140ステージをクリア</t>
+          <t>在试炼之路上完成第140关卡</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -34263,7 +34263,7 @@
       </c>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -34288,7 +34288,7 @@
       </c>
       <c r="Q333" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第150ステージをクリア</t>
+          <t>在试炼之路上完成第150关卡</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務</t>
+          <t>S级派遣任务</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -34385,7 +34385,7 @@
       </c>
       <c r="Q334" s="5" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務を10回クリア</t>
+          <t>完成10次S级派遣任务</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -34457,7 +34457,7 @@
       </c>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務</t>
+          <t>S级派遣任务</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="Q335" s="5" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務を20回クリア</t>
+          <t>完成20次S级派遣任务</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -34554,7 +34554,7 @@
       </c>
       <c r="L336" s="2" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務</t>
+          <t>S级派遣任务</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -34579,7 +34579,7 @@
       </c>
       <c r="Q336" s="5" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務を50回クリア</t>
+          <t>完成50次S级派遣任务</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -34651,7 +34651,7 @@
       </c>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務</t>
+          <t>S级派遣任务</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -34676,7 +34676,7 @@
       </c>
       <c r="Q337" s="5" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務を100回クリア</t>
+          <t>完成100次S级派遣任务</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -34748,7 +34748,7 @@
       </c>
       <c r="L338" s="2" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務</t>
+          <t>S级派遣任务</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -34773,7 +34773,7 @@
       </c>
       <c r="Q338" s="5" t="inlineStr">
         <is>
-          <t>Sランクの派遣任務を500回クリア</t>
+          <t>完成500次S级派遣任务</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -34845,7 +34845,7 @@
       </c>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務</t>
+          <t>S+级派遣任务</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -34870,7 +34870,7 @@
       </c>
       <c r="Q339" s="5" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務を10回クリア</t>
+          <t>完成10次S+等级派遣任务</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -34942,7 +34942,7 @@
       </c>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務</t>
+          <t>S+级派遣任务</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="Q340" s="5" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務を20回クリア</t>
+          <t>完成20次S+等级派遣任务</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務</t>
+          <t>S+级派遣任务</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="Q341" s="5" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務を50回クリア</t>
+          <t>完成50次S+等级派遣任务</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務</t>
+          <t>S+级派遣任务</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -35161,7 +35161,7 @@
       </c>
       <c r="Q342" s="5" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務を100回クリア</t>
+          <t>完成100次S+等级派遣任务</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -35233,7 +35233,7 @@
       </c>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務</t>
+          <t>S+级派遣任务</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="Q343" s="5" t="inlineStr">
         <is>
-          <t>S+ランクの派遣任務を500回クリア</t>
+          <t>完成500次S+等级派遣任务</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -35335,7 +35335,7 @@
       </c>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -35360,7 +35360,7 @@
       </c>
       <c r="Q344" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第160ステージをクリア</t>
+          <t>在试炼之路上完成第160关卡</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -35437,7 +35437,7 @@
       </c>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -35462,7 +35462,7 @@
       </c>
       <c r="Q345" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第170ステージをクリア</t>
+          <t>在试炼之路上完成第170关卡</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -35539,7 +35539,7 @@
       </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -35564,7 +35564,7 @@
       </c>
       <c r="Q346" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第180ステージをクリア</t>
+          <t>在试炼之路上完成第180关卡</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -35641,7 +35641,7 @@
       </c>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="Q347" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第190ステージをクリア</t>
+          <t>在考验之路上完成第190关卡</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -35748,7 +35748,7 @@
       </c>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -35773,7 +35773,7 @@
       </c>
       <c r="Q348" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第200ステージをクリア</t>
+          <t>在试炼之道完成第200关卡</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -35875,7 +35875,7 @@
       </c>
       <c r="Q349" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第210ステージをクリア</t>
+          <t>在试炼之道完成第210关卡</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -35952,7 +35952,7 @@
       </c>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -35977,7 +35977,7 @@
       </c>
       <c r="Q350" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第220ステージをクリア</t>
+          <t>在试炼之道完成第220关卡</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -36079,7 +36079,7 @@
       </c>
       <c r="Q351" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第230ステージをクリア</t>
+          <t>在考验之道完成第230关卡</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -36156,7 +36156,7 @@
       </c>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="Q352" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第240ステージをクリア</t>
+          <t>在试炼之道完成第240关卡</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -36258,7 +36258,7 @@
       </c>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -36283,7 +36283,7 @@
       </c>
       <c r="Q353" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第250ステージをクリア</t>
+          <t>在试炼之道完成第250关卡</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="Q354" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第260ステージをクリア</t>
+          <t>在试炼之道完成260关卡</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -36487,7 +36487,7 @@
       </c>
       <c r="Q355" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第270ステージをクリア</t>
+          <t>在考验之道完成第270关卡</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="L356" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -36589,7 +36589,7 @@
       </c>
       <c r="Q356" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第280ステージをクリア</t>
+          <t>在试炼之道完成第280关卡</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -36666,7 +36666,7 @@
       </c>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -36691,7 +36691,7 @@
       </c>
       <c r="Q357" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第290ステージをクリア</t>
+          <t>在试炼之道完成第290关卡</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -36773,7 +36773,7 @@
       </c>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -36798,7 +36798,7 @@
       </c>
       <c r="Q358" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第300ステージをクリア</t>
+          <t>在试炼之道完成第300关卡</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -36875,7 +36875,7 @@
       </c>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -36900,7 +36900,7 @@
       </c>
       <c r="Q359" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第310ステージをクリア</t>
+          <t>在试炼之道完成第310关卡</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
@@ -36977,7 +36977,7 @@
       </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -37002,7 +37002,7 @@
       </c>
       <c r="Q360" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第320ステージをクリア</t>
+          <t>在试炼之道完成第320关卡</t>
         </is>
       </c>
       <c r="R360" t="inlineStr">
@@ -37079,7 +37079,7 @@
       </c>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -37104,7 +37104,7 @@
       </c>
       <c r="Q361" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第330ステージをクリア</t>
+          <t>在试炼之道完成第330关卡</t>
         </is>
       </c>
       <c r="R361" t="inlineStr">
@@ -37181,7 +37181,7 @@
       </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -37206,7 +37206,7 @@
       </c>
       <c r="Q362" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第340ステージをクリア</t>
+          <t>在试炼之道完成第340关卡</t>
         </is>
       </c>
       <c r="R362" t="inlineStr">
@@ -37288,7 +37288,7 @@
       </c>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="Q363" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第350ステージをクリア</t>
+          <t>在试炼之道完成第350关卡</t>
         </is>
       </c>
       <c r="R363" t="inlineStr">
@@ -37390,7 +37390,7 @@
       </c>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="Q364" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第360ステージをクリア</t>
+          <t>在试炼之路上完成第360关卡</t>
         </is>
       </c>
       <c r="R364" t="inlineStr">
@@ -37492,7 +37492,7 @@
       </c>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -37517,7 +37517,7 @@
       </c>
       <c r="Q365" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第370ステージをクリア</t>
+          <t>在试炼之道完成第370关卡</t>
         </is>
       </c>
       <c r="R365" t="inlineStr">
@@ -37594,7 +37594,7 @@
       </c>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="Q366" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第380ステージをクリア</t>
+          <t>在试炼之道完成第380关卡</t>
         </is>
       </c>
       <c r="R366" t="inlineStr">
@@ -37696,7 +37696,7 @@
       </c>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -37721,7 +37721,7 @@
       </c>
       <c r="Q367" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第390ステージをクリア</t>
+          <t>在试炼之路上完成第390关卡</t>
         </is>
       </c>
       <c r="R367" t="inlineStr">
@@ -37803,7 +37803,7 @@
       </c>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="Q368" s="5" t="inlineStr">
         <is>
-          <t>試練の道で第400ステージをクリア</t>
+          <t>在试炼之路上完成第400关卡</t>
         </is>
       </c>
       <c r="R368" t="inlineStr">
@@ -41031,7 +41031,7 @@
       </c>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>闘志の芽生え</t>
+          <t>斗志的萌发</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
@@ -41056,7 +41056,7 @@
       </c>
       <c r="Q401" s="4" t="inlineStr">
         <is>
-          <t>アリーナで100回挑戦</t>
+          <t>在竞技场挑战100次</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>戦場の常連</t>
+          <t>战场上的常客</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
@@ -41153,7 +41153,7 @@
       </c>
       <c r="Q402" s="4" t="inlineStr">
         <is>
-          <t>アリーナで200回挑戦</t>
+          <t>在竞技场挑战200次</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
@@ -41225,7 +41225,7 @@
       </c>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>熟練の闘士</t>
+          <t>熟练的斗士</t>
         </is>
       </c>
       <c r="M403" t="inlineStr">
@@ -41250,7 +41250,7 @@
       </c>
       <c r="Q403" s="4" t="inlineStr">
         <is>
-          <t>アリーナで500回挑戦</t>
+          <t>在竞技场挑战500次</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
@@ -41322,7 +41322,7 @@
       </c>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>戦場の猛者</t>
+          <t>战场上的勇士</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -41347,7 +41347,7 @@
       </c>
       <c r="Q404" s="4" t="inlineStr">
         <is>
-          <t>アリーナで1000回挑戦</t>
+          <t>在竞技场挑战1000次</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>修羅の猛将</t>
+          <t>修罗猛将</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -41444,7 +41444,7 @@
       </c>
       <c r="Q405" s="4" t="inlineStr">
         <is>
-          <t>アリーナで2000回挑戦</t>
+          <t>在竞技场挑战2000次</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
@@ -41521,7 +41521,7 @@
       </c>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>アリーナ覇王</t>
+          <t>竞技场霸王</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -41546,7 +41546,7 @@
       </c>
       <c r="Q406" s="4" t="inlineStr">
         <is>
-          <t>アリーナで5000回挑戦</t>
+          <t>在竞技场挑战5000次</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
@@ -41618,7 +41618,7 @@
       </c>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>栄誉コイン</t>
+          <t>荣誉硬币</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -41643,7 +41643,7 @@
       </c>
       <c r="Q407" s="4" t="inlineStr">
         <is>
-          <t>栄誉コイン5000個を所有する</t>
+          <t>拥有5000枚荣誉金币</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
@@ -41715,7 +41715,7 @@
       </c>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>栄誉コイン</t>
+          <t>荣誉硬币</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
@@ -41740,7 +41740,7 @@
       </c>
       <c r="Q408" s="4" t="inlineStr">
         <is>
-          <t>栄誉コイン10000個を所有する</t>
+          <t>拥有10000枚荣誉硬币</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
@@ -41812,7 +41812,7 @@
       </c>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>栄誉コイン</t>
+          <t>荣誉硬币</t>
         </is>
       </c>
       <c r="M409" t="inlineStr">
@@ -41837,7 +41837,7 @@
       </c>
       <c r="Q409" s="4" t="inlineStr">
         <is>
-          <t>栄誉コイン50000個を所有する</t>
+          <t>拥有50000枚荣誉硬币</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
@@ -41909,7 +41909,7 @@
       </c>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>栄誉コイン</t>
+          <t>荣誉硬币</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -41934,7 +41934,7 @@
       </c>
       <c r="Q410" s="4" t="inlineStr">
         <is>
-          <t>栄誉コイン100000個を所有する</t>
+          <t>拥有荣誉硬币100000个</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
@@ -42006,7 +42006,7 @@
       </c>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>栄誉コイン</t>
+          <t>荣誉硬币</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -42031,7 +42031,7 @@
       </c>
       <c r="Q411" s="4" t="inlineStr">
         <is>
-          <t>栄誉コイン500000個を所有する</t>
+          <t>拥有500000个荣誉金币</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="L412" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -42133,7 +42133,7 @@
       </c>
       <c r="Q412" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル10回エントリー</t>
+          <t>精锐之战10次参赛</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
@@ -42210,7 +42210,7 @@
       </c>
       <c r="L413" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -42235,7 +42235,7 @@
       </c>
       <c r="Q413" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル50回エントリー</t>
+          <t>精锐之战50场</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
@@ -42312,7 +42312,7 @@
       </c>
       <c r="L414" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -42337,7 +42337,7 @@
       </c>
       <c r="Q414" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル100回エントリー</t>
+          <t>精锐战斗100回参赛名单</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
@@ -42414,7 +42414,7 @@
       </c>
       <c r="L415" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -42439,7 +42439,7 @@
       </c>
       <c r="Q415" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル200回エントリー</t>
+          <t>精英战斗200场比赛</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
@@ -42516,7 +42516,7 @@
       </c>
       <c r="L416" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -42541,7 +42541,7 @@
       </c>
       <c r="Q416" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル300回エントリー</t>
+          <t>精锐之战300场</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
@@ -42618,7 +42618,7 @@
       </c>
       <c r="L417" s="3" t="inlineStr">
         <is>
-          <t>精鋭対戦</t>
+          <t>精锐对战</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -42643,7 +42643,7 @@
       </c>
       <c r="Q417" s="4" t="inlineStr">
         <is>
-          <t>精鋭バトル500回エントリー</t>
+          <t>精锐之战500场</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
@@ -42718,7 +42718,7 @@
       </c>
       <c r="L419" s="2" t="inlineStr">
         <is>
-          <t>新しい友達</t>
+          <t>新好友</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -42743,7 +42743,7 @@
       </c>
       <c r="Q419" s="4" t="inlineStr">
         <is>
-          <t>友達を10人追加</t>
+          <t>添加10个好友</t>
         </is>
       </c>
       <c r="R419" t="inlineStr">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="L420" s="2" t="inlineStr">
         <is>
-          <t>コミュ神</t>
+          <t>交流之神</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="Q420" s="4" t="inlineStr">
         <is>
-          <t>友達を30人追加</t>
+          <t>新增30位好友</t>
         </is>
       </c>
       <c r="R420" t="inlineStr">
@@ -42927,7 +42927,7 @@
       </c>
       <c r="Q421" s="4" t="inlineStr">
         <is>
-          <t>友達を60人追加</t>
+          <t>新增60个好友</t>
         </is>
       </c>
       <c r="R421" t="inlineStr">
@@ -42994,7 +42994,7 @@
       </c>
       <c r="L422" s="2" t="inlineStr">
         <is>
-          <t>気遣いの芽</t>
+          <t>关心的萌芽</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -43019,7 +43019,7 @@
       </c>
       <c r="Q422" s="6" t="inlineStr">
         <is>
-          <t>体力を100回贈与</t>
+          <t>赠送100次体力</t>
         </is>
       </c>
       <c r="R422" t="inlineStr">
@@ -43086,7 +43086,7 @@
       </c>
       <c r="L423" s="2" t="inlineStr">
         <is>
-          <t>体力配り</t>
+          <t>体力分配</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -43111,7 +43111,7 @@
       </c>
       <c r="Q423" s="6" t="inlineStr">
         <is>
-          <t>体力を500回贈与</t>
+          <t>赠送500次体力</t>
         </is>
       </c>
       <c r="R423" t="inlineStr">
@@ -43178,7 +43178,7 @@
       </c>
       <c r="L424" s="2" t="inlineStr">
         <is>
-          <t>癒しの手</t>
+          <t>治愈之手</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -43203,7 +43203,7 @@
       </c>
       <c r="Q424" s="6" t="inlineStr">
         <is>
-          <t>体力を1000回贈与</t>
+          <t>赠送1000次体力</t>
         </is>
       </c>
       <c r="R424" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="Q425" s="6" t="inlineStr">
         <is>
-          <t>体力を2000回贈与</t>
+          <t>体力赠与2000次</t>
         </is>
       </c>
       <c r="R425" t="inlineStr">
@@ -43367,7 +43367,7 @@
       </c>
       <c r="L426" s="2" t="inlineStr">
         <is>
-          <t>支援の使徒</t>
+          <t>支持使徒</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -43392,7 +43392,7 @@
       </c>
       <c r="Q426" s="6" t="inlineStr">
         <is>
-          <t>体力を5000回贈与</t>
+          <t>体力赠与5000次</t>
         </is>
       </c>
       <c r="R426" t="inlineStr">
@@ -43459,7 +43459,7 @@
       </c>
       <c r="L427" s="2" t="inlineStr">
         <is>
-          <t>体力の守人</t>
+          <t>体力守护者</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -43484,7 +43484,7 @@
       </c>
       <c r="Q427" s="6" t="inlineStr">
         <is>
-          <t>体力を100回受け取る</t>
+          <t>获得100次体力</t>
         </is>
       </c>
       <c r="R427" t="inlineStr">
@@ -43551,7 +43551,7 @@
       </c>
       <c r="L428" s="2" t="inlineStr">
         <is>
-          <t>エナジーギヴァー</t>
+          <t>能量giver</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -43576,7 +43576,7 @@
       </c>
       <c r="Q428" s="6" t="inlineStr">
         <is>
-          <t>体力を600回受け取る</t>
+          <t>获得600次体力</t>
         </is>
       </c>
       <c r="R428" t="inlineStr">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="L429" s="2" t="inlineStr">
         <is>
-          <t>命脈の繋ぎ手</t>
+          <t>命脉的维系者</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -43668,7 +43668,7 @@
       </c>
       <c r="Q429" s="6" t="inlineStr">
         <is>
-          <t>体力を1800回受け取る</t>
+          <t>获得1800次体力</t>
         </is>
       </c>
       <c r="R429" t="inlineStr">
@@ -43735,7 +43735,7 @@
       </c>
       <c r="L430" s="2" t="inlineStr">
         <is>
-          <t>再生の光</t>
+          <t>再生之光</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -43760,7 +43760,7 @@
       </c>
       <c r="Q430" s="6" t="inlineStr">
         <is>
-          <t>体力を3600回受け取る</t>
+          <t>获得3600次体力</t>
         </is>
       </c>
       <c r="R430" t="inlineStr">
@@ -43827,7 +43827,7 @@
       </c>
       <c r="L431" s="2" t="inlineStr">
         <is>
-          <t>生命の恩人</t>
+          <t>救命恩人</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -43852,7 +43852,7 @@
       </c>
       <c r="Q431" s="6" t="inlineStr">
         <is>
-          <t>体力を7200回受け取る</t>
+          <t>获得7200次体力</t>
         </is>
       </c>
       <c r="R431" t="inlineStr">
@@ -43919,7 +43919,7 @@
       </c>
       <c r="L432" s="2" t="inlineStr">
         <is>
-          <t>ギルト貢献</t>
+          <t>吉尔特贡献</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -43944,7 +43944,7 @@
       </c>
       <c r="Q432" s="4" t="inlineStr">
         <is>
-          <t>ギルドでダイヤ寄付を累計100回行う</t>
+          <t>在公会累计捐赠100次钻石</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
@@ -44016,7 +44016,7 @@
       </c>
       <c r="L433" s="2" t="inlineStr">
         <is>
-          <t>ギルト貢献</t>
+          <t>吉尔特贡献</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -44041,7 +44041,7 @@
       </c>
       <c r="Q433" s="4" t="inlineStr">
         <is>
-          <t>ギルドでダイヤ寄付を累計500回行う</t>
+          <t>公会累计捐赠钻石500次</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
@@ -44113,7 +44113,7 @@
       </c>
       <c r="L434" s="2" t="inlineStr">
         <is>
-          <t>ギルト貢献</t>
+          <t>吉尔特贡献</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -44138,7 +44138,7 @@
       </c>
       <c r="Q434" s="4" t="inlineStr">
         <is>
-          <t>ギルドでダイヤ寄付を累計1000回行う</t>
+          <t>在公会累计捐赠1000次钻石</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
@@ -44210,7 +44210,7 @@
       </c>
       <c r="L435" s="2" t="inlineStr">
         <is>
-          <t>ギルト貢献</t>
+          <t>吉尔特贡献</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -44235,7 +44235,7 @@
       </c>
       <c r="Q435" s="4" t="inlineStr">
         <is>
-          <t>ギルドでダイヤ寄付を累計2000回行う</t>
+          <t>公会累计捐赠钻石2000次</t>
         </is>
       </c>
       <c r="R435" t="inlineStr">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="L436" s="2" t="inlineStr">
         <is>
-          <t>ギルトダイヤギフト</t>
+          <t>吉尔特钻石礼品</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -44332,7 +44332,7 @@
       </c>
       <c r="Q436" s="4" t="inlineStr">
         <is>
-          <t>ギルドのギフトを累計20回受け取る</t>
+          <t>累计获得20次公会礼物</t>
         </is>
       </c>
       <c r="R436" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="L437" s="2" t="inlineStr">
         <is>
-          <t>ギルトダイヤギフト</t>
+          <t>吉尔特钻石礼品</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -44429,7 +44429,7 @@
       </c>
       <c r="Q437" s="4" t="inlineStr">
         <is>
-          <t>ギルドのギフトを累計50回受け取る</t>
+          <t>累计获得50次公会礼物</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
@@ -44501,7 +44501,7 @@
       </c>
       <c r="L438" s="2" t="inlineStr">
         <is>
-          <t>ギルトダイヤギフト</t>
+          <t>吉尔特钻石礼品</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -44526,7 +44526,7 @@
       </c>
       <c r="Q438" s="4" t="inlineStr">
         <is>
-          <t>ギルドのギフトを累計100回受け取る</t>
+          <t>累计领取100件公会礼物</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="L439" s="2" t="inlineStr">
         <is>
-          <t>ギルトダイヤギフト</t>
+          <t>吉尔特钻石礼品</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -44623,7 +44623,7 @@
       </c>
       <c r="Q439" s="4" t="inlineStr">
         <is>
-          <t>ギルドのギフトを累計200回受け取る</t>
+          <t>累计领取200件公会礼物</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
@@ -44695,7 +44695,7 @@
       </c>
       <c r="L440" s="2" t="inlineStr">
         <is>
-          <t>ギルトダイヤギフト</t>
+          <t>吉尔特钻石礼品</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -44720,7 +44720,7 @@
       </c>
       <c r="Q440" s="4" t="inlineStr">
         <is>
-          <t>ギルドのギフトを累計500回受け取る</t>
+          <t>累计获得500件公会礼物</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
@@ -44800,7 +44800,7 @@
       </c>
       <c r="L442" s="2" t="inlineStr">
         <is>
-          <t>パワーブレイク</t>
+          <t>电源突破</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -44825,7 +44825,7 @@
       </c>
       <c r="Q442" s="4" t="inlineStr">
         <is>
-          <t>ダイヤ10連ガチャを累計50回する</t>
+          <t>钻石10连卡累计50次</t>
         </is>
       </c>
       <c r="R442" t="inlineStr">
@@ -44897,7 +44897,7 @@
       </c>
       <c r="L443" s="2" t="inlineStr">
         <is>
-          <t>ダブル召喚成功</t>
+          <t>双重召唤成功</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
@@ -44922,7 +44922,7 @@
       </c>
       <c r="Q443" s="4" t="inlineStr">
         <is>
-          <t>累計でダイヤ10連×10回、Sキャラ2体を同時獲得</t>
+          <t>累计钻石10连×10次，同时获得S角色2个</t>
         </is>
       </c>
       <c r="R443" t="inlineStr">
@@ -44994,7 +44994,7 @@
       </c>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>トリプル召喚成功</t>
+          <t>三重召唤成功</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -45019,7 +45019,7 @@
       </c>
       <c r="Q444" s="4" t="inlineStr">
         <is>
-          <t>累計でダイヤ10連×10回、Sキャラ3体を同時獲得</t>
+          <t>累计钻石10连×10次，同时获得S角色3尊</t>
         </is>
       </c>
       <c r="R444" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="L445" s="2" t="inlineStr">
         <is>
-          <t>ゴールドキング</t>
+          <t>黄金之王</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -45116,7 +45116,7 @@
       </c>
       <c r="Q445" s="4" t="inlineStr">
         <is>
-          <t>金貨で10連ガチャを累計1000回する</t>
+          <t>金币10连卡累计1000次</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
@@ -45183,7 +45183,7 @@
       </c>
       <c r="L446" s="2" t="inlineStr">
         <is>
-          <t>探索に夢中</t>
+          <t>热衷于探索</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -45208,7 +45208,7 @@
       </c>
       <c r="Q446" s="4" t="inlineStr">
         <is>
-          <t>探査機ガチャで5連ガチャを累計200回する</t>
+          <t>使用探测器转蛋累计5连转蛋200次</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="L447" s="2" t="inlineStr">
         <is>
-          <t>買い物好き</t>
+          <t>喜欢购物</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="Q447" s="6" t="inlineStr">
         <is>
-          <t>ショップを累計1000回更新する</t>
+          <t>商店累计更新1000次</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
@@ -45372,7 +45372,7 @@
       </c>
       <c r="L448" s="17" t="inlineStr">
         <is>
-          <t>称号収集</t>
+          <t>称号收集</t>
         </is>
       </c>
       <c r="M448" t="inlineStr">
@@ -45397,7 +45397,7 @@
       </c>
       <c r="Q448" s="4" t="inlineStr">
         <is>
-          <t>称号を累計40個獲得する</t>
+          <t>累计获得称号40个</t>
         </is>
       </c>
       <c r="R448" t="inlineStr">
@@ -45464,7 +45464,7 @@
       </c>
       <c r="L449" s="2" t="inlineStr">
         <is>
-          <t>アバター収集</t>
+          <t>头像收集</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -45489,7 +45489,7 @@
       </c>
       <c r="Q449" s="6" t="inlineStr">
         <is>
-          <t>アバターを累計10個解放する</t>
+          <t>累计释放10个头像</t>
         </is>
       </c>
       <c r="R449" t="inlineStr">
@@ -45556,7 +45556,7 @@
       </c>
       <c r="L450" s="2" t="inlineStr">
         <is>
-          <t>フレーム収集</t>
+          <t>框架收集</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="Q450" s="4" t="inlineStr">
         <is>
-          <t>フレームを累計10個アンロック</t>
+          <t>累计解锁10个框架</t>
         </is>
       </c>
       <c r="R450" t="inlineStr">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="L451" s="2" t="inlineStr">
         <is>
-          <t>アイコン収集</t>
+          <t>图标收集</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -45673,7 +45673,7 @@
       </c>
       <c r="Q451" s="4" t="inlineStr">
         <is>
-          <t>アイコンを累計250個アンロック</t>
+          <t>累计解锁250个图标</t>
         </is>
       </c>
       <c r="R451" t="inlineStr">
@@ -45740,7 +45740,7 @@
       </c>
       <c r="L452" s="2" t="inlineStr">
         <is>
-          <t>スタミナMAX</t>
+          <t>耐力MAX</t>
         </is>
       </c>
       <c r="M452" t="inlineStr">
@@ -45765,7 +45765,7 @@
       </c>
       <c r="Q452" s="6" t="inlineStr">
         <is>
-          <t>体力値が3000到達</t>
+          <t>体力值达到3000</t>
         </is>
       </c>
       <c r="R452" t="inlineStr">
@@ -45832,7 +45832,7 @@
       </c>
       <c r="L453" s="2" t="inlineStr">
         <is>
-          <t>メール爆弾</t>
+          <t>邮件炸弹</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -45857,7 +45857,7 @@
       </c>
       <c r="Q453" s="4" t="inlineStr">
         <is>
-          <t>メールが50件到達</t>
+          <t>收到50封邮件</t>
         </is>
       </c>
       <c r="R453" t="inlineStr">
@@ -46021,7 +46021,7 @@
       </c>
       <c r="L455" s="2" t="inlineStr">
         <is>
-          <t>魅力的な仲間</t>
+          <t>有魅力的伙伴</t>
         </is>
       </c>
       <c r="M455" t="inlineStr">
@@ -46046,7 +46046,7 @@
       </c>
       <c r="Q455" s="4" t="inlineStr">
         <is>
-          <t>ホーム画面キャラを2000回タッチ</t>
+          <t>触摸主屏幕角色2000次</t>
         </is>
       </c>
       <c r="R455" t="inlineStr">
@@ -46118,7 +46118,7 @@
       </c>
       <c r="L456" s="2" t="inlineStr">
         <is>
-          <t>無限トーク</t>
+          <t>无限谈话</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -46143,7 +46143,7 @@
       </c>
       <c r="Q456" s="4" t="inlineStr">
         <is>
-          <t>世界チャットで1000回発言</t>
+          <t>全球聊天1000次发言</t>
         </is>
       </c>
       <c r="R456" t="inlineStr">
@@ -46210,7 +46210,7 @@
       </c>
       <c r="L457" s="2" t="inlineStr">
         <is>
-          <t>大活躍中</t>
+          <t>大活跃中</t>
         </is>
       </c>
       <c r="M457" t="inlineStr">
@@ -46235,7 +46235,7 @@
       </c>
       <c r="Q457" s="4" t="inlineStr">
         <is>
-          <t>累計150日活躍度100到達</t>
+          <t>累计150天活跃度达到100</t>
         </is>
       </c>
       <c r="R457" t="inlineStr">
@@ -46302,7 +46302,7 @@
       </c>
       <c r="L458" s="2" t="inlineStr">
         <is>
-          <t>無尽の宝庫</t>
+          <t>无尽的宝库</t>
         </is>
       </c>
       <c r="M458" t="inlineStr">
@@ -46327,7 +46327,7 @@
       </c>
       <c r="Q458" s="4" t="inlineStr">
         <is>
-          <t>ダイヤでルーンガチャを累計5000個獲得</t>
+          <t>用钻石累计获得5000个符文卡</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="L460" s="18" t="inlineStr">
         <is>
-          <t>勝利！</t>
+          <t>胜利！</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
